--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +402 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +532 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +532 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +402 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +402 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +343 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime</t>
+          <t>loyer_estime · surface_a_ventiler · occupation_a_confirmer</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime · surface_a_ventiler · occupation_a_confirmer</t>
+          <t>loyer_estime · surface_a_ventiler</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>vous propose les murs de ce Local d'exception avec cuisine, douche et toilettes - Idéal cave à vin, atelier peinture, cours de musique ou activité premium Au coeur de Sèvres, dans un immeuble de caractère inspiré du style Louis XIV, découvrez ce local rare de 108 m², offrant un charme historique unique et des prestations pratiques pour une activité haut de gamme : cave à vin, galerie, atelier, showroom, espace de dégustation ou activité artisanale de prestige. Caractéristiques principales Surface totale : 108 m² Immeuble style Louis XIV : façade élégante, matériaux nobles, cachet exceptionnel</t>
+          <t>vous propose les murs de ce Local d'exception avec cuisine, douche et toilettes - Idéal cave à vin, atelier peinture, cours de musique ou activité premium Au coeur de Sèvres, dans un immeuble de caractère inspiré du style Louis XIV, découvrez ce local rare de 108 m², offrant un charme historique unique et des prestations pratiques pour une activité haut de gamme : cave à vin, galerie, atelier, showroom, espace de dégustation ou activité artisanale de prestige. Caractéristiques principales Surface totale : 108 m² Immeuble style Louis XIV : façade élégante, matériaux nobles, cachet exceptionnel Hauteur sous plafond généreuse Murs épais en pierre : atmosphère fraîche et stable, parfaite pour conservation de vins Accès indépendant Cuisine équipée (pratique pour dégustations, ateliers, événements) Douche + toilettes (rare pour un local de ce type, idéal pour activité nécessitant présence prolongée) Possibilité d'aménagement sur mesure selon l'activité Un lieu idéal pour une cave à vin haut de gamme Température naturellement stable Ambiance authentique et noble Possibilité d'aménager : espace de vieillissement salle de dégustation showroom pour bouteilles premium Cadre prestigieux pour une clientèle exigeante Parfait pour un caviste, sommelier, importateur, ou concept store autour du vin Localisation Sèvres, secteur recherché et résidentiel A proximité du Pont de Sèvres, Boulogne-Billancourt Transports : T2, métro, bus Environnement chic et dynamique Atouts investisseurs Murs libres Produit rare sur le marché Forte demande pour locaux de caractère Potentiel de valorisation élevé Convient aussi pour profession libérale ou activité artistique AMARA F., au . Selon l'article L.561.5 du Code Monétaire et Financier, pour l'organisation de la visite, la présentation d'une pièce d'identité vous sera demandée. Cette présente annonce a été rédigée sous la responsabilité éditoriale de AMARA F., immatriculé au RSAC NANTERRE 902745389 auprès de , au capital de 44 920 euros, - ; SIRET 4 040, RCS Nantes. Carte Professionnelle Transactions sur immeubles et fonds de commerce (T) et Gestion immobilière (G) n°20 8 délivrée par la - Saint Nazaire. . -SMABTP - 89 rue de la Boétie, 75008 Paris pour 2 000 000 euros pour T et 120 000 euros pour G. Assurance responsabilité civile professionnelle par GALIAN-SMABTP n° de police RCP_01_28137J. Mandat réf : 106B-AFAT - Le professionnel garantit et sécurise votre projet immobilier. A (EI) Agent Commercial - Numéro RSAC : NANTERRE 902745389 - . Les informations sur les risques auxquels ce bien est exposé sont disponibles sur le site Géorisques : georisques. gouv. fr</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-sevres-acc9397a.xlsx
+++ b/docs/dossiers/dossier-sevres-acc9397a.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
